--- a/test_receipt_20260312_112705_入库.xlsx
+++ b/test_receipt_20260312_112705_入库.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>商品条码</t>
   </si>
@@ -1067,125 +1067,34 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" t="s">
         <v>10</v>
       </c>
     </row>
